--- a/业务场景.xlsx
+++ b/业务场景.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="按菜单拆分功能与场景" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="功能清单对照" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,8 +104,23 @@
       <color rgb="0064748B"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -151,8 +167,28 @@
         <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -247,11 +283,25 @@
         <color rgb="0094A3B8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,6 +369,27 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -685,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1679,8 +1750,8 @@
       <c r="K30" s="10" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="13" t="n"/>
-      <c r="B31" s="13" t="n"/>
+      <c r="A31" s="12" t="n"/>
+      <c r="B31" s="12" t="n"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
           <t>27</t>
@@ -1821,8 +1892,8 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="13" t="n"/>
-      <c r="B35" s="13" t="n"/>
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
           <t>3</t>
@@ -2084,7 +2155,7 @@
           <t>工程支撑</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n"/>
+      <c r="B43" s="11" t="n"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
           <t>—</t>
@@ -2211,6 +2282,989 @@
       <c r="A51" s="25" t="inlineStr">
         <is>
           <t>人天口径与原业务场景表完全一致，仅重新编排；"上传同步表清单"与勾选同界面未加额外人天（如需 Excel 模板上传增强：+1 FE +1 BE）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>后续 / 二期（未计入当前合计 120.5 人天）— 对照《功能清单.xlsx》确认未覆盖、本次按“缓/后期”保留的功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>前端菜单</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>功能分组（操作步骤）</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>步骤</t>
+        </is>
+      </c>
+      <c r="D54" s="27" t="inlineStr">
+        <is>
+          <t>业务功能</t>
+        </is>
+      </c>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>技术功能（服务/实现层）</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G54" s="27" t="inlineStr">
+        <is>
+          <t>前端(React)</t>
+        </is>
+      </c>
+      <c r="H54" s="27" t="inlineStr">
+        <is>
+          <t>后端API(.NET)</t>
+        </is>
+      </c>
+      <c r="I54" s="27" t="inlineStr">
+        <is>
+          <t>数据(Databricks)</t>
+        </is>
+      </c>
+      <c r="J54" s="27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="K54" s="27" t="inlineStr">
+        <is>
+          <t>技术要点 / 备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 迁移完整性</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>迁移数据完整性校验（迁移前基准记录+迁移后比对+一致性报告）</t>
+        </is>
+      </c>
+      <c r="E55" s="29" t="inlineStr">
+        <is>
+          <t>清单 6/7/8 · 退役合规审计</t>
+        </is>
+      </c>
+      <c r="F55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 合规保留</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="inlineStr">
+        <is>
+          <t>Legal Hold 冻结（涉诉/审计/合规调查中暂停删除与修改）</t>
+        </is>
+      </c>
+      <c r="E56" s="29" t="inlineStr">
+        <is>
+          <t>清单 48</t>
+        </is>
+      </c>
+      <c r="F56" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 到期处置</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="inlineStr">
+        <is>
+          <t>保留到期自动删除 + 删除/保留策略变更审批留痕</t>
+        </is>
+      </c>
+      <c r="E57" s="29" t="inlineStr">
+        <is>
+          <t>清单 47/42/43 · 现规划为校验后手动删除</t>
+        </is>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 检索导出</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="29" t="inlineStr">
+        <is>
+          <t>检索结果导出(Excel/CSV/PDF)+加密字段导出控制+导出审计</t>
+        </is>
+      </c>
+      <c r="E58" s="29" t="inlineStr">
+        <is>
+          <t>清单 67/66/21</t>
+        </is>
+      </c>
+      <c r="F58" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 统计台账</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="inlineStr">
+        <is>
+          <t>归档统计台账(按系统/时间/类型统计容量)+报表导出</t>
+        </is>
+      </c>
+      <c r="E59" s="29" t="inlineStr">
+        <is>
+          <t>清单 22-25</t>
+        </is>
+      </c>
+      <c r="F59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 元数据治理</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>元数据批量补全/修正工具</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>清单 36</t>
+        </is>
+      </c>
+      <c r="F60" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 全文检索</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>全文/关键词跨档案检索(标题/元数据/OCR)</t>
+        </is>
+      </c>
+      <c r="E61" s="29" t="inlineStr">
+        <is>
+          <t>清单 14</t>
+        </is>
+      </c>
+      <c r="F61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B62" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 细粒度权限</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D62" s="29" t="inlineStr">
+        <is>
+          <t>记录级/字段级数据访问权限 + 权限申请/变更审批流</t>
+        </is>
+      </c>
+      <c r="E62" s="29" t="inlineStr">
+        <is>
+          <t>清单 82-85</t>
+        </is>
+      </c>
+      <c r="F62" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B63" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 脱敏增强</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>手动选脱敏字段 / 策略按角色生效 / 脱敏预览 + 脱敏日志</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>清单 51-54/69 · 核心脱敏已含</t>
+        </is>
+      </c>
+      <c r="F63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B64" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 离线包导入</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D64" s="29" t="inlineStr">
+        <is>
+          <t>非结构化离线介质/压缩包批量导入增强</t>
+        </is>
+      </c>
+      <c r="E64" s="29" t="inlineStr">
+        <is>
+          <t>清单 3 · 在线附件迁移已含</t>
+        </is>
+      </c>
+      <c r="F64" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 备份恢复</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D65" s="29" t="inlineStr">
+        <is>
+          <t>数据备份管理 / 异地灾备 / 恢复演练</t>
+        </is>
+      </c>
+      <c r="E65" s="29" t="inlineStr">
+        <is>
+          <t>清单 55-57 · 基建类</t>
+        </is>
+      </c>
+      <c r="F65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 存储性能</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D66" s="29" t="inlineStr">
+        <is>
+          <t>存储策略优化 / 查询性能优化 / 系统监控告警 / 稳定性保障</t>
+        </is>
+      </c>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>清单 50/68/80/81</t>
+        </is>
+      </c>
+      <c r="F66" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B67" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 集成连接器</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="29" t="inlineStr">
+        <is>
+          <t>第三方集成工具适配 / 标准接口 / 连接器模板与监控审计</t>
+        </is>
+      </c>
+      <c r="E67" s="29" t="inlineStr">
+        <is>
+          <t>清单 73/75-79</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B68" s="28" t="inlineStr">
+        <is>
+          <t>二期 · 个性化</t>
+        </is>
+      </c>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>个性化页面/视图/检索条件保存/页面模板(可选)</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>清单 58-62</t>
+        </is>
+      </c>
+      <c r="F68" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B69" s="28" t="inlineStr">
+        <is>
+          <t>后续 · AI 智能化(整组)</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>AI：智能解析/自动分类/语义检索/自然语言问答/智能报表/风险预警等</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>清单 Phase3 全组 · 未逐条确认，二期后评估</t>
+        </is>
+      </c>
+      <c r="F69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B70" s="28" t="inlineStr">
+        <is>
+          <t>忽略 · 非当前范围</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>在运系统增量同步 / 在运冷数据识别与接入 / 冷数据分类与生命周期 / 档案目录</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>不适用于退役归档，忽略</t>
+        </is>
+      </c>
+      <c r="F70" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="29" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>说明：本区为对照《功能清单》识别出的“现规划未覆盖/缺口”项，经确认为二期或后续，均未计入上方合计 120.5 人天。</t>
         </is>
       </c>
     </row>
@@ -2239,4 +3293,4620 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H111"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>《功能清单》× 现规划(业务场景.xlsx)对照表 · 范围=退役归档主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>口径：现状以 业务场景.xlsx 现有规划（120.5人天已含步骤）为“现有”；未覆盖项经确认归二期/后续或忽略；AI 整组后续未逐条确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>功能清单·阶段</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>功能模块</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>业务场景(清单)</t>
+        </is>
+      </c>
+      <c r="D3" s="27" t="inlineStr">
+        <is>
+          <t>关键功能</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>具体功能</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="inlineStr">
+        <is>
+          <t>现状(对照现规划)</t>
+        </is>
+      </c>
+      <c r="G3" s="27" t="inlineStr">
+        <is>
+          <t>处理 / 去向</t>
+        </is>
+      </c>
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>模块 1：存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>退役系统历史数据全量入库归档</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>结构化历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>现规划经 勾选表→ETL/归档执行 结构化入库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>模块 1：存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>退役系统历史数据全量入库归档</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>非结构化文件及离线包批量导入</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H5" s="29" t="inlineStr">
+        <is>
+          <t>在线附件迁移已含；离线介质/压缩包批量导入为二期增强</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>模块 1：存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>退役系统历史数据全量入库归档</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>迁移规则配置</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>数据导入规则配置</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="inlineStr">
+        <is>
+          <t>转换/脱敏/附件URL/ETL 规则配置已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>模块 1：存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>退役系统历史数据全量入库归档</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>迁移任务管理</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>导入任务调度与监控</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="inlineStr">
+        <is>
+          <t>归档执行/批次管理/结果查看/失败重试已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>模块 1：存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>确保迁移过程数据完整可追溯</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>迁移完整性校验</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>迁移前完整性基准记录</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H8" s="29" t="inlineStr">
+        <is>
+          <t>二期·迁移完整性（迁移前基准记录）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>模块 1：存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>确保迁移过程数据完整可追溯</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>迁移完整性校验</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>迁移后完整性比对</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="inlineStr">
+        <is>
+          <t>二期·迁移完整性（迁移后比对）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>模块 1：存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>确保迁移过程数据完整可追溯</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>迁移完整性校验</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>迁移一致性报告</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="inlineStr">
+        <is>
+          <t>二期·迁移完整性（一致性报告）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>异构数据统一归档至标准档案模型</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>标准归档模型管理</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>标准归档对象定义</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="inlineStr">
+        <is>
+          <t>归档对象/归档集(r_archive_set)等已建模</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>异构数据统一归档至标准档案模型</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>标准归档模型管理</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
+        <is>
+          <t>归档目录结构管理</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H12" s="29" t="inlineStr">
+        <is>
+          <t>传统档案目录/章节折叠夹，结构化归档不适用，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>满足数据不出境和本地化合规要求</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>境内数据驻留管理</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>境内数据驻留部署</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>Azure 中国境内部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>满足数据不出境和本地化合规要求</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>数据加密与密钥管理</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>数据加密存储</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="inlineStr">
+        <is>
+          <t>字段加解密 + 存储/传输加密</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>满足数据不出境和本地化合规要求</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>数据加密与密钥管理</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>密钥管理</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="inlineStr">
+        <is>
+          <t>Key Vault 密钥管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>基础档案检索</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>关键词检索</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="inlineStr">
+        <is>
+          <t>结构化字段查询已有；跨档案 OCR 全文关键词为二期</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>基础档案检索</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>按系统名称检索</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H17" s="29" t="inlineStr">
+        <is>
+          <t>按系统检索已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>基础档案检索</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="inlineStr">
+        <is>
+          <t>按业务时间检索</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H18" s="29" t="inlineStr">
+        <is>
+          <t>按业务时间检索已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>检索结果展示与预览</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>检索结果列表展示</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="inlineStr">
+        <is>
+          <t>列表展示/排序/关键字段已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="inlineStr">
+        <is>
+          <t>检索结果展示与预览</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>原始文件在线预览</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H20" s="29" t="inlineStr">
+        <is>
+          <t>附件 SAS 直链在线预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>用户操作审计追踪</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>归档操作日志记录</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="inlineStr">
+        <is>
+          <t>审计日志(操作/删除)已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>用户操作审计追踪</t>
+        </is>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
+        <is>
+          <t>查询操作日志记录</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H22" s="29" t="inlineStr">
+        <is>
+          <t>查询行为日志已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>用户操作审计追踪</t>
+        </is>
+      </c>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t>导出操作日志记录</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G23" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="inlineStr">
+        <is>
+          <t>二期·检索导出(导出操作日志)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>退役系统归档数据统一台账</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>归档统计与基础报表</t>
+        </is>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
+        <is>
+          <t>按系统统计归档数据量</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="inlineStr">
+        <is>
+          <t>二期·归档统计台账(按系统)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>退役系统归档数据统一台账</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>归档统计与基础报表</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>按时间统计归档数据量</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G25" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>二期·归档统计台账(按时间)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>退役系统归档数据统一台账</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="inlineStr">
+        <is>
+          <t>归档统计与基础报表</t>
+        </is>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
+        <is>
+          <t>按数据类型统计归档量</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H26" s="29" t="inlineStr">
+        <is>
+          <t>二期·归档统计台账(按类型)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>退役系统归档数据统一台账</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>归档统计与基础报表</t>
+        </is>
+      </c>
+      <c r="E27" s="29" t="inlineStr">
+        <is>
+          <t>基础报表导出</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="inlineStr">
+        <is>
+          <t>二期·台账报表导出</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>用户与角色管理</t>
+        </is>
+      </c>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>基础角色权限配置</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="inlineStr">
+        <is>
+          <t>基础角色权限配置已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>用户与角色管理</t>
+        </is>
+      </c>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t>用户账号管理</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H29" s="29" t="inlineStr">
+        <is>
+          <t>用户账号管理已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>企业用户统一身份认证与系统访问</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
+        <is>
+          <t>SSO 单点登录</t>
+        </is>
+      </c>
+      <c r="E30" s="29" t="inlineStr">
+        <is>
+          <t>企业SSO集成</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G30" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H30" s="29" t="inlineStr">
+        <is>
+          <t>企业 SSO 集成已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>企业用户统一身份认证与系统访问</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>SSO 单点登录</t>
+        </is>
+      </c>
+      <c r="E31" s="29" t="inlineStr">
+        <is>
+          <t>用户身份自动识别与关联</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H31" s="29" t="inlineStr">
+        <is>
+          <t>SSO 身份→用户/角色关联已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>企业用户统一身份认证与系统访问</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr">
+        <is>
+          <t>SSO 单点登录</t>
+        </is>
+      </c>
+      <c r="E32" s="29" t="inlineStr">
+        <is>
+          <t>登录状态与异常访问控制</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="inlineStr">
+        <is>
+          <t>登录状态/失效/异常访问基础控制已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>多源异构数据接入与元数据标准化规整</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>元数据标准与来源管理</t>
+        </is>
+      </c>
+      <c r="E33" s="29" t="inlineStr">
+        <is>
+          <t>统一元数据模型</t>
+        </is>
+      </c>
+      <c r="F33" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G33" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H33" s="29" t="inlineStr">
+        <is>
+          <t>Schema Registry 统一元数据模型驱动</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>多源异构数据接入与元数据标准化规整</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="inlineStr">
+        <is>
+          <t>元数据标准与来源管理</t>
+        </is>
+      </c>
+      <c r="E34" s="29" t="inlineStr">
+        <is>
+          <t>来源系统信息绑定</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H34" s="29" t="inlineStr">
+        <is>
+          <t>来源系统编码/绑定已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>在运系统低频冷数据迁移</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="inlineStr">
+        <is>
+          <t>冷数据识别与接入</t>
+        </is>
+      </c>
+      <c r="E35" s="29" t="inlineStr">
+        <is>
+          <t>冷数据识别与标记</t>
+        </is>
+      </c>
+      <c r="F35" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G35" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="inlineStr">
+        <is>
+          <t>在运系统冷数据识别，不适用退役，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>在运系统低频冷数据迁移</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="inlineStr">
+        <is>
+          <t>冷数据识别与接入</t>
+        </is>
+      </c>
+      <c r="E36" s="29" t="inlineStr">
+        <is>
+          <t>在运系统冷数据周期性接入</t>
+        </is>
+      </c>
+      <c r="F36" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G36" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="inlineStr">
+        <is>
+          <t>在运冷数据周期接入，不适用退役，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>提升数据规整度与查阅效率</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="inlineStr">
+        <is>
+          <t>数据质量管理</t>
+        </is>
+      </c>
+      <c r="E37" s="29" t="inlineStr">
+        <is>
+          <t>数据质量评分</t>
+        </is>
+      </c>
+      <c r="F37" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H37" s="29" t="inlineStr">
+        <is>
+          <t>AI 整组，二期后评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>提升数据规整度与查阅效率</t>
+        </is>
+      </c>
+      <c r="D38" s="29" t="inlineStr">
+        <is>
+          <t>数据质量管理</t>
+        </is>
+      </c>
+      <c r="E38" s="29" t="inlineStr">
+        <is>
+          <t>元数据补全与修正</t>
+        </is>
+      </c>
+      <c r="F38" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G38" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H38" s="29" t="inlineStr">
+        <is>
+          <t>二期·元数据批量补全/修正工具</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>在运系统增量数据实时同步</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="inlineStr">
+        <is>
+          <t>增量数据同步</t>
+        </is>
+      </c>
+      <c r="E39" s="29" t="inlineStr">
+        <is>
+          <t>数据库增量数据同步</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G39" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H39" s="29" t="inlineStr">
+        <is>
+          <t>在运增量同步，不适用退役，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>在运系统增量数据实时同步</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="inlineStr">
+        <is>
+          <t>增量数据同步</t>
+        </is>
+      </c>
+      <c r="E40" s="29" t="inlineStr">
+        <is>
+          <t>业务事件触发同步</t>
+        </is>
+      </c>
+      <c r="F40" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G40" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="inlineStr">
+        <is>
+          <t>在运业务事件触发同步，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>在运系统增量数据实时同步</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>增量数据同步</t>
+        </is>
+      </c>
+      <c r="E41" s="29" t="inlineStr">
+        <is>
+          <t>文件增量同步</t>
+        </is>
+      </c>
+      <c r="F41" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G41" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H41" s="29" t="inlineStr">
+        <is>
+          <t>在运文件增量同步，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>在运系统低频冷数据迁移</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="inlineStr">
+        <is>
+          <t>冷数据归档与生命周期管理</t>
+        </is>
+      </c>
+      <c r="E42" s="29" t="inlineStr">
+        <is>
+          <t>冷数据分类归档</t>
+        </is>
+      </c>
+      <c r="F42" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G42" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H42" s="29" t="inlineStr">
+        <is>
+          <t>在运冷数据分类归档，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>在运系统低频冷数据迁移</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>冷数据归档与生命周期管理</t>
+        </is>
+      </c>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>冷数据生命周期管理</t>
+        </is>
+      </c>
+      <c r="F43" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G43" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H43" s="29" t="inlineStr">
+        <is>
+          <t>在运冷数据生命周期，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>关键操作合规审批</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="inlineStr">
+        <is>
+          <t>保留与处置策略审批</t>
+        </is>
+      </c>
+      <c r="E44" s="29" t="inlineStr">
+        <is>
+          <t>删除审批与操作留痕</t>
+        </is>
+      </c>
+      <c r="F44" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G44" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H44" s="29" t="inlineStr">
+        <is>
+          <t>二期·删除审批与操作留痕(后期再做)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>关键操作合规审批</t>
+        </is>
+      </c>
+      <c r="D45" s="29" t="inlineStr">
+        <is>
+          <t>保留与处置策略审批</t>
+        </is>
+      </c>
+      <c r="E45" s="29" t="inlineStr">
+        <is>
+          <t>保留策略变更审批流</t>
+        </is>
+      </c>
+      <c r="F45" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G45" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="inlineStr">
+        <is>
+          <t>二期·保留策略变更审批流(随#3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>标准化数据组装为归档对象</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="inlineStr">
+        <is>
+          <t>标准归档转换与校验</t>
+        </is>
+      </c>
+      <c r="E46" s="29" t="inlineStr">
+        <is>
+          <t>标准数据归档对象转换</t>
+        </is>
+      </c>
+      <c r="F46" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G46" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H46" s="29" t="inlineStr">
+        <is>
+          <t>ETL→标准归档对象转换已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>源系统数据结构自动映射归档</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="inlineStr">
+        <is>
+          <t>标准归档转换与校验</t>
+        </is>
+      </c>
+      <c r="E47" s="29" t="inlineStr">
+        <is>
+          <t>归档规则自动应用</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G47" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H47" s="29" t="inlineStr">
+        <is>
+          <t>归档规则自动应用已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>源系统数据结构自动映射归档</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>标准归档转换与校验</t>
+        </is>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>归档结果校验</t>
+        </is>
+      </c>
+      <c r="F48" s="34" t="inlineStr">
+        <is>
+          <t>部分覆盖</t>
+        </is>
+      </c>
+      <c r="G48" s="28" t="inlineStr">
+        <is>
+          <t>现规划含基础，增强入二期</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="inlineStr">
+        <is>
+          <t>执行结果核对已含；深度完整性比对见二期#6-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>归档记录定期删除与合规保留</t>
+        </is>
+      </c>
+      <c r="D49" s="29" t="inlineStr">
+        <is>
+          <t>到期处置与Legal Hold管理</t>
+        </is>
+      </c>
+      <c r="E49" s="29" t="inlineStr">
+        <is>
+          <t>保留期限到期自动删除</t>
+        </is>
+      </c>
+      <c r="F49" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G49" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="inlineStr">
+        <is>
+          <t>二期·保留到期自动删除</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>模块 3：记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>归档记录定期删除与合规保留</t>
+        </is>
+      </c>
+      <c r="D50" s="29" t="inlineStr">
+        <is>
+          <t>到期处置与Legal Hold管理</t>
+        </is>
+      </c>
+      <c r="E50" s="29" t="inlineStr">
+        <is>
+          <t>Legal Hold 冻结</t>
+        </is>
+      </c>
+      <c r="F50" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G50" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="inlineStr">
+        <is>
+          <t>二期·Legal Hold 冻结</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>在运系统低频冷数据迁移</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>分层存储与策略优化</t>
+        </is>
+      </c>
+      <c r="E51" s="29" t="inlineStr">
+        <is>
+          <t>冷热数据分层存储</t>
+        </is>
+      </c>
+      <c r="F51" s="33" t="inlineStr">
+        <is>
+          <t>非当前范围</t>
+        </is>
+      </c>
+      <c r="G51" s="28" t="inlineStr">
+        <is>
+          <t>不适用退役归档 · 忽略</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="inlineStr">
+        <is>
+          <t>冷热分层属在运冷数据承接，忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>保障系统稳定运行与查询性能</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="inlineStr">
+        <is>
+          <t>分层存储与策略优化</t>
+        </is>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
+        <is>
+          <t>存储策略优化</t>
+        </is>
+      </c>
+      <c r="F52" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G52" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="inlineStr">
+        <is>
+          <t>二期·存储策略优化(低优先)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>敏感历史数据字段级脱敏</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="inlineStr">
+        <is>
+          <t>字段级数据脱敏管理</t>
+        </is>
+      </c>
+      <c r="E53" s="29" t="inlineStr">
+        <is>
+          <t>字段级脱敏规则配置</t>
+        </is>
+      </c>
+      <c r="F53" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G53" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H53" s="29" t="inlineStr">
+        <is>
+          <t>敏感字段标识+脱敏规则配置(字段级核心)已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>敏感历史数据字段级脱敏</t>
+        </is>
+      </c>
+      <c r="D54" s="29" t="inlineStr">
+        <is>
+          <t>字段级数据脱敏管理</t>
+        </is>
+      </c>
+      <c r="E54" s="29" t="inlineStr">
+        <is>
+          <t>手动选择脱敏字段</t>
+        </is>
+      </c>
+      <c r="F54" s="34" t="inlineStr">
+        <is>
+          <t>部分覆盖</t>
+        </is>
+      </c>
+      <c r="G54" s="28" t="inlineStr">
+        <is>
+          <t>现规划含基础，增强入二期</t>
+        </is>
+      </c>
+      <c r="H54" s="29" t="inlineStr">
+        <is>
+          <t>手动选择脱敏字段为二期增强</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>敏感历史数据字段级脱敏</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>字段级数据脱敏管理</t>
+        </is>
+      </c>
+      <c r="E55" s="29" t="inlineStr">
+        <is>
+          <t>脱敏策略应用</t>
+        </is>
+      </c>
+      <c r="F55" s="34" t="inlineStr">
+        <is>
+          <t>部分覆盖</t>
+        </is>
+      </c>
+      <c r="G55" s="28" t="inlineStr">
+        <is>
+          <t>现规划含基础，增强入二期</t>
+        </is>
+      </c>
+      <c r="H55" s="29" t="inlineStr">
+        <is>
+          <t>脱敏策略按记录/角色生效为二期增强</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B56" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>敏感历史数据字段级脱敏</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="inlineStr">
+        <is>
+          <t>字段级数据脱敏管理</t>
+        </is>
+      </c>
+      <c r="E56" s="29" t="inlineStr">
+        <is>
+          <t>脱敏预览</t>
+        </is>
+      </c>
+      <c r="F56" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G56" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H56" s="29" t="inlineStr">
+        <is>
+          <t>二期·脱敏预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B57" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="inlineStr">
+        <is>
+          <t>确保归档数据可恢复</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="inlineStr">
+        <is>
+          <t>数据备份与灾难恢复</t>
+        </is>
+      </c>
+      <c r="E57" s="29" t="inlineStr">
+        <is>
+          <t>数据备份管理</t>
+        </is>
+      </c>
+      <c r="F57" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G57" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H57" s="29" t="inlineStr">
+        <is>
+          <t>二期·数据备份管理(基建)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B58" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>确保归档数据可恢复</t>
+        </is>
+      </c>
+      <c r="D58" s="29" t="inlineStr">
+        <is>
+          <t>数据备份与灾难恢复</t>
+        </is>
+      </c>
+      <c r="E58" s="29" t="inlineStr">
+        <is>
+          <t>异地灾备</t>
+        </is>
+      </c>
+      <c r="F58" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G58" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H58" s="29" t="inlineStr">
+        <is>
+          <t>二期·异地灾备(基建)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B59" s="29" t="inlineStr">
+        <is>
+          <t>模块 4：数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>确保归档数据可恢复</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="inlineStr">
+        <is>
+          <t>数据备份与灾难恢复</t>
+        </is>
+      </c>
+      <c r="E59" s="29" t="inlineStr">
+        <is>
+          <t>恢复演练</t>
+        </is>
+      </c>
+      <c r="F59" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G59" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H59" s="29" t="inlineStr">
+        <is>
+          <t>二期·恢复演练(基建)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>不同岗位个性化查询页面</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>个性化页面与视图管理</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>自定义页面布局</t>
+        </is>
+      </c>
+      <c r="F60" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G60" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H60" s="29" t="inlineStr">
+        <is>
+          <t>二期·个性化页面(可选)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B61" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>不同岗位个性化查询页面</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>个性化页面与视图管理</t>
+        </is>
+      </c>
+      <c r="E61" s="29" t="inlineStr">
+        <is>
+          <t>自定义展示字段</t>
+        </is>
+      </c>
+      <c r="F61" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G61" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H61" s="29" t="inlineStr">
+        <is>
+          <t>二期·自定义展示字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B62" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>不同岗位个性化查询页面</t>
+        </is>
+      </c>
+      <c r="D62" s="29" t="inlineStr">
+        <is>
+          <t>个性化页面与视图管理</t>
+        </is>
+      </c>
+      <c r="E62" s="29" t="inlineStr">
+        <is>
+          <t>可配置化页面能力</t>
+        </is>
+      </c>
+      <c r="F62" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G62" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H62" s="29" t="inlineStr">
+        <is>
+          <t>二期·检索条件保存复用</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>不同岗位个性化查询页面</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>个性化页面与视图管理</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>用户个人视图保存</t>
+        </is>
+      </c>
+      <c r="F63" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G63" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H63" s="29" t="inlineStr">
+        <is>
+          <t>二期·个人视图保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>不同岗位个性化查询页面</t>
+        </is>
+      </c>
+      <c r="D64" s="29" t="inlineStr">
+        <is>
+          <t>个性化页面与视图管理</t>
+        </is>
+      </c>
+      <c r="E64" s="29" t="inlineStr">
+        <is>
+          <t>页面模板管理</t>
+        </is>
+      </c>
+      <c r="F64" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G64" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H64" s="29" t="inlineStr">
+        <is>
+          <t>二期·页面模板管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B65" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C65" s="29" t="inlineStr">
+        <is>
+          <t>业务人员精细化、个性化查询</t>
+        </is>
+      </c>
+      <c r="D65" s="29" t="inlineStr">
+        <is>
+          <t>高级检索与筛选</t>
+        </is>
+      </c>
+      <c r="E65" s="29" t="inlineStr">
+        <is>
+          <t>多维度组合检索</t>
+        </is>
+      </c>
+      <c r="F65" s="34" t="inlineStr">
+        <is>
+          <t>部分覆盖</t>
+        </is>
+      </c>
+      <c r="G65" s="28" t="inlineStr">
+        <is>
+          <t>现规划含基础，增强入二期</t>
+        </is>
+      </c>
+      <c r="H65" s="29" t="inlineStr">
+        <is>
+          <t>动态查询已支持多字段组合筛选；复杂组合/精准入二期</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>业务人员精细化、个性化查询</t>
+        </is>
+      </c>
+      <c r="D66" s="29" t="inlineStr">
+        <is>
+          <t>高级检索与筛选</t>
+        </is>
+      </c>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>精准筛选</t>
+        </is>
+      </c>
+      <c r="F66" s="34" t="inlineStr">
+        <is>
+          <t>部分覆盖</t>
+        </is>
+      </c>
+      <c r="G66" s="28" t="inlineStr">
+        <is>
+          <t>现规划含基础，增强入二期</t>
+        </is>
+      </c>
+      <c r="H66" s="29" t="inlineStr">
+        <is>
+          <t>同#63</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B67" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C67" s="29" t="inlineStr">
+        <is>
+          <t>业务人员精细化、个性化查询</t>
+        </is>
+      </c>
+      <c r="D67" s="29" t="inlineStr">
+        <is>
+          <t>高级检索与筛选</t>
+        </is>
+      </c>
+      <c r="E67" s="29" t="inlineStr">
+        <is>
+          <t>模糊全文检索</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G67" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H67" s="29" t="inlineStr">
+        <is>
+          <t>二期·模糊全文/拼音检索</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>业务人员精细化、个性化查询</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>检索结果导出</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>加密字段导出控制</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G68" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>二期·加密字段导出控制(检索导出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>Phase1：基础归档与查询</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>业务人员精细化、个性化查询</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>检索结果导出</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>检索文档结果导出</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G69" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>二期·检索文档结果导出</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B70" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>保障系统稳定运行与查询性能</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>查询性能管理</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>查询性能优化</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G70" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H70" s="29" t="inlineStr">
+        <is>
+          <t>二期·查询性能优化(基建)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B71" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>敏感历史数据字段级脱敏</t>
+        </is>
+      </c>
+      <c r="D71" s="29" t="inlineStr">
+        <is>
+          <t>合规操作审计与复核</t>
+        </is>
+      </c>
+      <c r="E71" s="29" t="inlineStr">
+        <is>
+          <t>脱敏日志记录</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G71" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H71" s="29" t="inlineStr">
+        <is>
+          <t>二期·脱敏日志记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B72" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>按角色控制数据访问范围</t>
+        </is>
+      </c>
+      <c r="D72" s="29" t="inlineStr">
+        <is>
+          <t>合规操作审计与复核</t>
+        </is>
+      </c>
+      <c r="E72" s="29" t="inlineStr">
+        <is>
+          <t>权限审计与复核</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G72" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H72" s="29" t="inlineStr">
+        <is>
+          <t>二期·权限审计与复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B73" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>多类型标准化接口对接</t>
+        </is>
+      </c>
+      <c r="D73" s="29" t="inlineStr">
+        <is>
+          <t>多源数据连接管理</t>
+        </is>
+      </c>
+      <c r="E73" s="29" t="inlineStr">
+        <is>
+          <t>标准数据库连接能力</t>
+        </is>
+      </c>
+      <c r="F73" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G73" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H73" s="29" t="inlineStr">
+        <is>
+          <t>标准 DB 连接(迁移用)已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B74" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>多类型标准化接口对接</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="inlineStr">
+        <is>
+          <t>多源数据连接管理</t>
+        </is>
+      </c>
+      <c r="E74" s="29" t="inlineStr">
+        <is>
+          <t>标准文件连接能力</t>
+        </is>
+      </c>
+      <c r="F74" s="28" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="G74" s="28" t="inlineStr">
+        <is>
+          <t>现规划内（已计入 120.5 人天）</t>
+        </is>
+      </c>
+      <c r="H74" s="29" t="inlineStr">
+        <is>
+          <t>标准文件/对象存储连接(附件)已含</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B75" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>第三方集成工具兼容</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="inlineStr">
+        <is>
+          <t>多源数据连接管理</t>
+        </is>
+      </c>
+      <c r="E75" s="29" t="inlineStr">
+        <is>
+          <t>第三方数据集成工具适配</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G75" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H75" s="29" t="inlineStr">
+        <is>
+          <t>二期·第三方集成工具适配</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>建立统一集成标准，规范上游源系统唯一标识与跨系统数据交互格式</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>集成标准与接口管理</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>固定源系统编码规则</t>
+        </is>
+      </c>
+      <c r="F76" s="34" t="inlineStr">
+        <is>
+          <t>部分覆盖</t>
+        </is>
+      </c>
+      <c r="G76" s="28" t="inlineStr">
+        <is>
+          <t>现规划含基础，增强入二期</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>源系统编码已建立；交互格式规范增强入二期</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>建立统一集成标准，规范上游源系统唯一标识与跨系统数据交互格式</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>集成标准与接口管理</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>统一数据交互格式规范</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G77" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>二期·统一数据交互格式规范</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>多类型标准化接口对接</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="inlineStr">
+        <is>
+          <t>集成标准与接口管理</t>
+        </is>
+      </c>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>标准系统接口能力</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G78" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H78" s="29" t="inlineStr">
+        <is>
+          <t>二期·标准系统接口能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B79" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C79" s="29" t="inlineStr">
+        <is>
+          <t>降低多系统对接改造成本</t>
+        </is>
+      </c>
+      <c r="D79" s="29" t="inlineStr">
+        <is>
+          <t>连接器模板管理</t>
+        </is>
+      </c>
+      <c r="E79" s="29" t="inlineStr">
+        <is>
+          <t>连接器模板库与复用</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G79" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H79" s="29" t="inlineStr">
+        <is>
+          <t>二期·连接器模板库与复用</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B80" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C80" s="29" t="inlineStr">
+        <is>
+          <t>连接器统一运维</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="inlineStr">
+        <is>
+          <t>连接器运行监控与审计</t>
+        </is>
+      </c>
+      <c r="E80" s="29" t="inlineStr">
+        <is>
+          <t>连接器状态监控</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G80" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H80" s="29" t="inlineStr">
+        <is>
+          <t>二期·连接器状态监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B81" s="29" t="inlineStr">
+        <is>
+          <t>模块 7：多源系统集成与标准化连接器</t>
+        </is>
+      </c>
+      <c r="C81" s="29" t="inlineStr">
+        <is>
+          <t>连接器统一运维</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>连接器运行监控与审计</t>
+        </is>
+      </c>
+      <c r="E81" s="29" t="inlineStr">
+        <is>
+          <t>连接器日志与审计</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G81" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H81" s="29" t="inlineStr">
+        <is>
+          <t>二期·连接器日志与审计</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B82" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>保障系统稳定运行与查询性能</t>
+        </is>
+      </c>
+      <c r="D82" s="29" t="inlineStr">
+        <is>
+          <t>系统运行监控与稳定性保障</t>
+        </is>
+      </c>
+      <c r="E82" s="29" t="inlineStr">
+        <is>
+          <t>系统监控告警</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G82" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H82" s="29" t="inlineStr">
+        <is>
+          <t>二期·系统监控告警(DevOps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B83" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>保障系统稳定运行与查询性能</t>
+        </is>
+      </c>
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>系统运行监控与稳定性保障</t>
+        </is>
+      </c>
+      <c r="E83" s="29" t="inlineStr">
+        <is>
+          <t>系统稳定性保障</t>
+        </is>
+      </c>
+      <c r="F83" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G83" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H83" s="29" t="inlineStr">
+        <is>
+          <t>二期·系统稳定性保障(DevOps/基建)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B84" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C84" s="29" t="inlineStr">
+        <is>
+          <t>按角色控制数据访问范围</t>
+        </is>
+      </c>
+      <c r="D84" s="29" t="inlineStr">
+        <is>
+          <t>细粒度数据访问控制</t>
+        </is>
+      </c>
+      <c r="E84" s="29" t="inlineStr">
+        <is>
+          <t>记录级权限控制</t>
+        </is>
+      </c>
+      <c r="F84" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G84" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H84" s="29" t="inlineStr">
+        <is>
+          <t>二期·记录级权限控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B85" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C85" s="29" t="inlineStr">
+        <is>
+          <t>按角色控制数据访问范围</t>
+        </is>
+      </c>
+      <c r="D85" s="29" t="inlineStr">
+        <is>
+          <t>细粒度数据访问控制</t>
+        </is>
+      </c>
+      <c r="E85" s="29" t="inlineStr">
+        <is>
+          <t>字段级权限控制</t>
+        </is>
+      </c>
+      <c r="F85" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G85" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H85" s="29" t="inlineStr">
+        <is>
+          <t>二期·字段级权限控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B86" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C86" s="29" t="inlineStr">
+        <is>
+          <t>按角色控制数据访问范围</t>
+        </is>
+      </c>
+      <c r="D86" s="29" t="inlineStr">
+        <is>
+          <t>权限申请与变更审批</t>
+        </is>
+      </c>
+      <c r="E86" s="29" t="inlineStr">
+        <is>
+          <t>权限申请与审批</t>
+        </is>
+      </c>
+      <c r="F86" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G86" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H86" s="29" t="inlineStr">
+        <is>
+          <t>二期·权限申请与审批</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr">
+        <is>
+          <t>Phase2：能力优化与冷数据承接</t>
+        </is>
+      </c>
+      <c r="B87" s="29" t="inlineStr">
+        <is>
+          <t>模块 8：系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C87" s="29" t="inlineStr">
+        <is>
+          <t>关键操作合规审批</t>
+        </is>
+      </c>
+      <c r="D87" s="29" t="inlineStr">
+        <is>
+          <t>权限申请与变更审批</t>
+        </is>
+      </c>
+      <c r="E87" s="29" t="inlineStr">
+        <is>
+          <t>权限变更审批流</t>
+        </is>
+      </c>
+      <c r="F87" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G87" s="28" t="inlineStr">
+        <is>
+          <t>二期 / 后续（本次确认：缓/后期）</t>
+        </is>
+      </c>
+      <c r="H87" s="29" t="inlineStr">
+        <is>
+          <t>二期·权限变更审批流</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B88" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C88" s="29" t="inlineStr">
+        <is>
+          <t>自动提取附件与数据中的业务信息</t>
+        </is>
+      </c>
+      <c r="D88" s="29" t="inlineStr">
+        <is>
+          <t>智能内容解析与信息提取</t>
+        </is>
+      </c>
+      <c r="E88" s="29" t="inlineStr">
+        <is>
+          <t>文档内容自动解析</t>
+        </is>
+      </c>
+      <c r="F88" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G88" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H88" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B89" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C89" s="29" t="inlineStr">
+        <is>
+          <t>自动提取附件与数据中的业务信息</t>
+        </is>
+      </c>
+      <c r="D89" s="29" t="inlineStr">
+        <is>
+          <t>智能内容解析与信息提取</t>
+        </is>
+      </c>
+      <c r="E89" s="29" t="inlineStr">
+        <is>
+          <t>结构化数据自动解析</t>
+        </is>
+      </c>
+      <c r="F89" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G89" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H89" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B90" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C90" s="29" t="inlineStr">
+        <is>
+          <t>自动提取附件与数据中的业务信息</t>
+        </is>
+      </c>
+      <c r="D90" s="29" t="inlineStr">
+        <is>
+          <t>智能内容解析与信息提取</t>
+        </is>
+      </c>
+      <c r="E90" s="29" t="inlineStr">
+        <is>
+          <t>核心业务信息提取</t>
+        </is>
+      </c>
+      <c r="F90" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G90" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H90" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B91" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C91" s="29" t="inlineStr">
+        <is>
+          <t>自动提取附件与数据中的业务信息</t>
+        </is>
+      </c>
+      <c r="D91" s="29" t="inlineStr">
+        <is>
+          <t>智能内容解析与信息提取</t>
+        </is>
+      </c>
+      <c r="E91" s="29" t="inlineStr">
+        <is>
+          <t>解析结果人工校验</t>
+        </is>
+      </c>
+      <c r="F91" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G91" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H91" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B92" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C92" s="29" t="inlineStr">
+        <is>
+          <t>海量归档数据自动规整</t>
+        </is>
+      </c>
+      <c r="D92" s="29" t="inlineStr">
+        <is>
+          <t>智能分类与语义标签</t>
+        </is>
+      </c>
+      <c r="E92" s="29" t="inlineStr">
+        <is>
+          <t>基于AI的自动分类</t>
+        </is>
+      </c>
+      <c r="F92" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G92" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H92" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B93" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C93" s="29" t="inlineStr">
+        <is>
+          <t>海量归档数据自动规整</t>
+        </is>
+      </c>
+      <c r="D93" s="29" t="inlineStr">
+        <is>
+          <t>智能分类与语义标签</t>
+        </is>
+      </c>
+      <c r="E93" s="29" t="inlineStr">
+        <is>
+          <t>AI语义标签生成</t>
+        </is>
+      </c>
+      <c r="F93" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G93" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H93" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B94" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C94" s="29" t="inlineStr">
+        <is>
+          <t>海量归档数据自动规整</t>
+        </is>
+      </c>
+      <c r="D94" s="29" t="inlineStr">
+        <is>
+          <t>数据质量管理</t>
+        </is>
+      </c>
+      <c r="E94" s="29" t="inlineStr">
+        <is>
+          <t>重复数据识别</t>
+        </is>
+      </c>
+      <c r="F94" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G94" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H94" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B95" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C95" s="29" t="inlineStr">
+        <is>
+          <t>海量归档数据自动规整</t>
+        </is>
+      </c>
+      <c r="D95" s="29" t="inlineStr">
+        <is>
+          <t>数据关联关系智能挖掘</t>
+        </is>
+      </c>
+      <c r="E95" s="29" t="inlineStr">
+        <is>
+          <t>数据关联关系挖掘</t>
+        </is>
+      </c>
+      <c r="F95" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G95" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H95" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B96" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C96" s="29" t="inlineStr">
+        <is>
+          <t>海量归档数据自动规整</t>
+        </is>
+      </c>
+      <c r="D96" s="29" t="inlineStr">
+        <is>
+          <t>智能分类与语义标签</t>
+        </is>
+      </c>
+      <c r="E96" s="29" t="inlineStr">
+        <is>
+          <t>分类结果人工确认</t>
+        </is>
+      </c>
+      <c r="F96" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G96" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H96" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B97" s="29" t="inlineStr">
+        <is>
+          <t>模块 2：实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C97" s="29" t="inlineStr">
+        <is>
+          <t>合规核查与风险预警</t>
+        </is>
+      </c>
+      <c r="D97" s="29" t="inlineStr">
+        <is>
+          <t>数据质量管理</t>
+        </is>
+      </c>
+      <c r="E97" s="29" t="inlineStr">
+        <is>
+          <t>异常数据识别</t>
+        </is>
+      </c>
+      <c r="F97" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G97" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H97" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B98" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C98" s="29" t="inlineStr">
+        <is>
+          <t>突破关键词检索限制</t>
+        </is>
+      </c>
+      <c r="D98" s="29" t="inlineStr">
+        <is>
+          <t>智能语义检索与匹配</t>
+        </is>
+      </c>
+      <c r="E98" s="29" t="inlineStr">
+        <is>
+          <t>语义检索</t>
+        </is>
+      </c>
+      <c r="F98" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G98" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H98" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B99" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C99" s="29" t="inlineStr">
+        <is>
+          <t>突破关键词检索限制</t>
+        </is>
+      </c>
+      <c r="D99" s="29" t="inlineStr">
+        <is>
+          <t>智能语义检索与匹配</t>
+        </is>
+      </c>
+      <c r="E99" s="29" t="inlineStr">
+        <is>
+          <t>模糊智能匹配</t>
+        </is>
+      </c>
+      <c r="F99" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G99" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H99" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B100" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C100" s="29" t="inlineStr">
+        <is>
+          <t>突破关键词检索限制</t>
+        </is>
+      </c>
+      <c r="D100" s="29" t="inlineStr">
+        <is>
+          <t>关联档案智能推荐</t>
+        </is>
+      </c>
+      <c r="E100" s="29" t="inlineStr">
+        <is>
+          <t>关联数据智能推荐</t>
+        </is>
+      </c>
+      <c r="F100" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G100" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H100" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B101" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C101" s="29" t="inlineStr">
+        <is>
+          <t>突破关键词检索限制</t>
+        </is>
+      </c>
+      <c r="D101" s="29" t="inlineStr">
+        <is>
+          <t>档案自然语言问答</t>
+        </is>
+      </c>
+      <c r="E101" s="29" t="inlineStr">
+        <is>
+          <t>自然语言问答</t>
+        </is>
+      </c>
+      <c r="F101" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G101" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H101" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B102" s="29" t="inlineStr">
+        <is>
+          <t>模块 5：档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C102" s="29" t="inlineStr">
+        <is>
+          <t>突破关键词检索限制</t>
+        </is>
+      </c>
+      <c r="D102" s="29" t="inlineStr">
+        <is>
+          <t>搜索结果智能排序</t>
+        </is>
+      </c>
+      <c r="E102" s="29" t="inlineStr">
+        <is>
+          <t>搜索结果智能排序</t>
+        </is>
+      </c>
+      <c r="F102" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G102" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H102" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B103" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C103" s="29" t="inlineStr">
+        <is>
+          <t>合规核查与风险预警</t>
+        </is>
+      </c>
+      <c r="D103" s="29" t="inlineStr">
+        <is>
+          <t>智能合规风险识别与提醒</t>
+        </is>
+      </c>
+      <c r="E103" s="29" t="inlineStr">
+        <is>
+          <t>留存周期智能提醒</t>
+        </is>
+      </c>
+      <c r="F103" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G103" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H103" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B104" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C104" s="29" t="inlineStr">
+        <is>
+          <t>合规核查与风险预警</t>
+        </is>
+      </c>
+      <c r="D104" s="29" t="inlineStr">
+        <is>
+          <t>智能合规风险识别与提醒</t>
+        </is>
+      </c>
+      <c r="E104" s="29" t="inlineStr">
+        <is>
+          <t>合规风险预警</t>
+        </is>
+      </c>
+      <c r="F104" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G104" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H104" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B105" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C105" s="29" t="inlineStr">
+        <is>
+          <t>合规核查与风险预警</t>
+        </is>
+      </c>
+      <c r="D105" s="29" t="inlineStr">
+        <is>
+          <t>智能审计建议生成</t>
+        </is>
+      </c>
+      <c r="E105" s="29" t="inlineStr">
+        <is>
+          <t>审计建议生成</t>
+        </is>
+      </c>
+      <c r="F105" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G105" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H105" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B106" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C106" s="29" t="inlineStr">
+        <is>
+          <t>合规核查与风险预警</t>
+        </is>
+      </c>
+      <c r="D106" s="29" t="inlineStr">
+        <is>
+          <t>智能合规风险识别与提醒</t>
+        </is>
+      </c>
+      <c r="E106" s="29" t="inlineStr">
+        <is>
+          <t>敏感信息识别</t>
+        </is>
+      </c>
+      <c r="F106" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G106" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H106" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B107" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C107" s="29" t="inlineStr">
+        <is>
+          <t>自动生成归档数据报告</t>
+        </is>
+      </c>
+      <c r="D107" s="29" t="inlineStr">
+        <is>
+          <t>智能报表与分析生成</t>
+        </is>
+      </c>
+      <c r="E107" s="29" t="inlineStr">
+        <is>
+          <t>归档数据智能报表</t>
+        </is>
+      </c>
+      <c r="F107" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G107" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H107" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B108" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C108" s="29" t="inlineStr">
+        <is>
+          <t>自动生成归档数据报告</t>
+        </is>
+      </c>
+      <c r="D108" s="29" t="inlineStr">
+        <is>
+          <t>智能报表与分析生成</t>
+        </is>
+      </c>
+      <c r="E108" s="29" t="inlineStr">
+        <is>
+          <t>审计台账自动生成</t>
+        </is>
+      </c>
+      <c r="F108" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G108" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H108" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B109" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C109" s="29" t="inlineStr">
+        <is>
+          <t>自动生成归档数据报告</t>
+        </is>
+      </c>
+      <c r="D109" s="29" t="inlineStr">
+        <is>
+          <t>智能报表与分析生成</t>
+        </is>
+      </c>
+      <c r="E109" s="29" t="inlineStr">
+        <is>
+          <t>业务复盘数据生成</t>
+        </is>
+      </c>
+      <c r="F109" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G109" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H109" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B110" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C110" s="29" t="inlineStr">
+        <is>
+          <t>自动生成归档数据报告</t>
+        </is>
+      </c>
+      <c r="D110" s="29" t="inlineStr">
+        <is>
+          <t>智能报表与分析生成</t>
+        </is>
+      </c>
+      <c r="E110" s="29" t="inlineStr">
+        <is>
+          <t>数据趋势智能分析</t>
+        </is>
+      </c>
+      <c r="F110" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G110" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H110" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="28" t="inlineStr">
+        <is>
+          <t>Phase3：AI智能化赋能</t>
+        </is>
+      </c>
+      <c r="B111" s="29" t="inlineStr">
+        <is>
+          <t>模块 6：合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C111" s="29" t="inlineStr">
+        <is>
+          <t>自动生成归档数据报告</t>
+        </is>
+      </c>
+      <c r="D111" s="29" t="inlineStr">
+        <is>
+          <t>报告自动生成与分发</t>
+        </is>
+      </c>
+      <c r="E111" s="29" t="inlineStr">
+        <is>
+          <t>报告自动分发</t>
+        </is>
+      </c>
+      <c r="F111" s="32" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="G111" s="28" t="inlineStr">
+        <is>
+          <t>AI 智能化 · 后续（未逐条确认）</t>
+        </is>
+      </c>
+      <c r="H111" s="29" t="inlineStr">
+        <is>
+          <t>AI 智能化整组，二期后评估，未逐条确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>